--- a/tanoshimi/docs/02_요구사항정의서.xlsx
+++ b/tanoshimi/docs/02_요구사항정의서.xlsx
@@ -4302,12 +4302,12 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>여행 리마인더</t>
+          <t xml:space="preserve">여행 리마인더 (제거됨)</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>출발이 임박한 파티원에게 스케줄러가 매일 알림을 생성한다.</t>
+          <t xml:space="preserve">⛔ 제거됨 — 예약(출발일) 데이터에 의존해 결제·예약 제거와 함께 스케줄러(TripReminderScheduler) 삭제. notifyTripReminder 설정 토글만 잔존(향후 재도입 대비).</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t xml:space="preserve">제거</t>
         </is>
       </c>
     </row>
